--- a/astro-site/public/dl/plan-negocio-finca-eventos-bodas/calculadora-presupuesto-boda-evento-finca.xlsx
+++ b/astro-site/public/dl/plan-negocio-finca-eventos-bodas/calculadora-presupuesto-boda-evento-finca.xlsx
@@ -1410,7 +1410,7 @@
         <v>5399.625</v>
       </c>
     </row>
-    <row r="64" ht="16" customHeight="1">
+    <row r="64" ht="30" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Importe retenido si cancela: tramo 5</t>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Último tramo, hasta el día del evento.</t>
+          <t>Último tramo, hasta el día del evento. Con particulares, el contrato descuenta de este importe los costes que la finca se ahorra por no celebrarlo.</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="16" customHeight="1">
+    <row r="121" ht="30" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
           <t>Cancelación tramo 5: lo que retienes (% del total)</t>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Último mes o no presentación: el 100 %.</t>
+          <t>Último mes o no presentación: el 100 %. Con particulares, el contrato descuenta los costes que la finca se ahorra por no celebrarlo.</t>
         </is>
       </c>
     </row>
